--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -2092,7 +2092,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:30</t>
+          <t>2026-02-28 19:01:05</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:30</t>
+          <t>2026-02-28 19:01:05</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:31</t>
+          <t>2026-02-28 19:01:06</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:31</t>
+          <t>2026-02-28 19:01:06</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:31</t>
+          <t>2026-02-28 19:01:06</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:32</t>
+          <t>2026-02-28 19:01:07</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:32</t>
+          <t>2026-02-28 19:01:07</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:32</t>
+          <t>2026-02-28 19:01:07</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:33</t>
+          <t>2026-02-28 19:01:08</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:33</t>
+          <t>2026-02-28 19:01:08</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:33</t>
+          <t>2026-02-28 19:01:08</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:34</t>
+          <t>2026-02-28 19:01:09</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:34</t>
+          <t>2026-02-28 19:01:09</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:34</t>
+          <t>2026-02-28 19:01:09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-02-28 17:17:35</t>
+          <t>2026-02-28 19:01:09</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -5569,233 +5569,215 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF92D050"/>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AN41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="21.4609375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="2" max="7"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="8" max="8"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="9" max="11"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="12" max="12"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="10" min="13" max="13"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="14" max="27"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="28" max="28"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="29" max="32"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="33" max="33"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="34" max="34"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="35" max="35"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="36" max="36"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="37" max="37"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="38" max="40"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="3">
-      <c r="A1" s="26" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Part Number</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>Category of product (MCU, MPU, Sensor, Analogic, Power, Passive Component, Transceiver Wireless)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>Country of Manufacturing Plant 1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>Country of Manufacturing Plant 2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>Country of Manufacturing Plant 3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="33" t="inlineStr">
         <is>
           <t>Country of Manufacturing Plant 4</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H1" s="33" t="inlineStr">
         <is>
           <t>Supplier Lead Time (weeks)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="33" t="inlineStr">
         <is>
           <t>Proprietary (Y/N)**</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="33" t="inlineStr">
         <is>
           <t>Commodity (Y/N)*</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="33" t="inlineStr">
         <is>
           <t>Stand-Alone Functional Device (Y/N)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="33" t="inlineStr">
         <is>
           <t>Weeks to qualify</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="33" t="inlineStr">
         <is>
           <t>Unit Price ($)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="33" t="inlineStr">
         <is>
           <t>Specify Certification/Qualification</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="33" t="inlineStr">
         <is>
           <t>In case answer on Column C is Y, Which other device in the BOM is necessary to run the PN on Column B? (e.g. PMIC for MPU, Memory for MPU)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="33" t="inlineStr">
         <is>
           <t>Created_at</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="33" t="inlineStr">
         <is>
           <t>Updated_at</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="33" t="inlineStr">
         <is>
           <t>Frontend_Country</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="33" t="inlineStr">
         <is>
           <t>Backend_Country</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="33" t="inlineStr">
         <is>
           <t>Technology_Node</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="33" t="inlineStr">
         <is>
           <t>Plant_1_Name</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="33" t="inlineStr">
         <is>
           <t>Plant_2_Name</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="33" t="inlineStr">
         <is>
           <t>Plant_3_Name</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="33" t="inlineStr">
         <is>
           <t>Plant_4_Name</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="33" t="inlineStr">
         <is>
           <t>EMS_Used</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="33" t="inlineStr">
         <is>
           <t>EMS_Name</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="33" t="inlineStr">
         <is>
           <t>EMS_Location</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AB1" s="33" t="inlineStr">
         <is>
           <t>SW_Code_Size_KB</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="33" t="inlineStr">
         <is>
           <t>Memory_Type</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="33" t="inlineStr">
         <is>
           <t>OS_Type</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="33" t="inlineStr">
         <is>
           <t>Wireless_Protocol</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="33" t="inlineStr">
         <is>
           <t>EOL_Status</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AG1" s="33" t="inlineStr">
         <is>
           <t>Number_of_Alternative_Sources</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="33" t="inlineStr">
         <is>
           <t>Supplier_Financial_Health</t>
         </is>
       </c>
-      <c r="AI1" s="4" t="inlineStr">
+      <c r="AI1" s="33" t="inlineStr">
         <is>
           <t>MTBF_Hours</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="33" t="inlineStr">
         <is>
           <t>Automotive_Grade</t>
         </is>
       </c>
-      <c r="AK1" s="4" t="inlineStr">
+      <c r="AK1" s="33" t="inlineStr">
         <is>
           <t>Last_Price_Increase_Pct</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="33" t="inlineStr">
         <is>
           <t>Allocation_Status</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="33" t="inlineStr">
         <is>
           <t>Package_Type</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="33" t="inlineStr">
         <is>
           <t>Supported_Interfaces</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" s="3">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>MKE02Z64VLD4</t>
@@ -5816,7 +5798,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" t="n">
         <v>18</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -5834,10 +5816,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" s="8" t="n">
+      <c r="M2" t="n">
         <v>0.85</v>
       </c>
       <c r="N2" t="inlineStr">
@@ -5870,13 +5852,12 @@
           <t>90nm</t>
         </is>
       </c>
-      <c r="AB2" s="9" t="n"/>
       <c r="AF2" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG2" s="5" t="n">
+      <c r="AG2" t="n">
         <v>3</v>
       </c>
       <c r="AH2" t="inlineStr">
@@ -5884,10 +5865,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI2" s="5" t="n">
+      <c r="AI2" t="n">
         <v>500000</v>
       </c>
-      <c r="AK2" s="5" t="n">
+      <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="inlineStr">
@@ -5901,7 +5882,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" s="3">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>STM32MP157CAC3</t>
@@ -5922,7 +5903,7 @@
           <t>France</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" t="n">
         <v>24</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -5940,10 +5921,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" t="n">
         <v>32</v>
       </c>
-      <c r="M3" s="8" t="n">
+      <c r="M3" t="n">
         <v>12.5</v>
       </c>
       <c r="N3" t="inlineStr">
@@ -5981,13 +5962,12 @@
           <t>40nm</t>
         </is>
       </c>
-      <c r="AB3" s="9" t="n"/>
       <c r="AF3" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG3" s="5" t="n">
+      <c r="AG3" t="n">
         <v>1</v>
       </c>
       <c r="AH3" t="inlineStr">
@@ -5995,10 +5975,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI3" s="5" t="n">
+      <c r="AI3" t="n">
         <v>300000</v>
       </c>
-      <c r="AK3" s="5" t="n">
+      <c r="AK3" t="n">
         <v>5</v>
       </c>
       <c r="AL3" t="inlineStr">
@@ -6012,7 +5992,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" s="3">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>STPMIC1APQR</t>
@@ -6033,7 +6013,7 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" t="n">
         <v>20</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -6051,10 +6031,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" t="n">
         <v>28</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" t="n">
         <v>4.2</v>
       </c>
       <c r="N4" t="inlineStr">
@@ -6092,13 +6072,12 @@
           <t>130nm</t>
         </is>
       </c>
-      <c r="AB4" s="9" t="n"/>
       <c r="AF4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG4" s="5" t="n">
+      <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
@@ -6106,10 +6085,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI4" s="5" t="n">
+      <c r="AI4" t="n">
         <v>400000</v>
       </c>
-      <c r="AK4" s="5" t="n">
+      <c r="AK4" t="n">
         <v>8</v>
       </c>
       <c r="AL4" t="inlineStr">
@@ -6123,7 +6102,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" s="3">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>BME280</t>
@@ -6149,7 +6128,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" t="n">
         <v>12</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -6167,10 +6146,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" t="n">
         <v>2.1</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -6198,13 +6177,12 @@
           <t>MEMS</t>
         </is>
       </c>
-      <c r="AB5" s="9" t="n"/>
       <c r="AF5" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG5" s="5" t="n">
+      <c r="AG5" t="n">
         <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
@@ -6212,10 +6190,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI5" s="5" t="n">
+      <c r="AI5" t="n">
         <v>200000</v>
       </c>
-      <c r="AK5" s="5" t="n">
+      <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="inlineStr">
@@ -6229,7 +6207,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" s="3">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>ESP32-WROOM-32E</t>
@@ -6255,7 +6233,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" t="n">
         <v>16</v>
       </c>
       <c r="I6" t="inlineStr">
@@ -6273,10 +6251,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" t="n">
         <v>20</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" t="n">
         <v>3.5</v>
       </c>
       <c r="N6" t="inlineStr">
@@ -6309,13 +6287,12 @@
           <t>40nm</t>
         </is>
       </c>
-      <c r="AB6" s="9" t="n"/>
       <c r="AF6" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG6" s="5" t="n">
+      <c r="AG6" t="n">
         <v>1</v>
       </c>
       <c r="AH6" t="inlineStr">
@@ -6323,10 +6300,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI6" s="5" t="n">
+      <c r="AI6" t="n">
         <v>250000</v>
       </c>
-      <c r="AK6" s="5" t="n">
+      <c r="AK6" t="n">
         <v>12</v>
       </c>
       <c r="AL6" t="inlineStr">
@@ -6340,7 +6317,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" s="3">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>GRM155R71C104KA88D</t>
@@ -6371,7 +6348,7 @@
           <t>Philippines</t>
         </is>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="inlineStr">
@@ -6389,10 +6366,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" t="n">
         <v>0.02</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -6420,13 +6397,12 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="AB7" s="9" t="n"/>
       <c r="AF7" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="n">
+      <c r="AG7" t="n">
         <v>5</v>
       </c>
       <c r="AH7" t="inlineStr">
@@ -6434,10 +6410,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="n">
+      <c r="AI7" t="n">
         <v>1000000</v>
       </c>
-      <c r="AK7" s="5" t="n">
+      <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="inlineStr">
@@ -6451,7 +6427,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" s="3">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>TPS62840DLCR</t>
@@ -6482,7 +6458,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" t="n">
         <v>10</v>
       </c>
       <c r="I8" t="inlineStr">
@@ -6500,10 +6476,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" t="n">
         <v>1.85</v>
       </c>
       <c r="P8" t="inlineStr">
@@ -6531,13 +6507,12 @@
           <t>65nm</t>
         </is>
       </c>
-      <c r="AB8" s="9" t="n"/>
       <c r="AF8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG8" s="5" t="n">
+      <c r="AG8" t="n">
         <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
@@ -6545,10 +6520,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI8" s="5" t="n">
+      <c r="AI8" t="n">
         <v>600000</v>
       </c>
-      <c r="AK8" s="5" t="n">
+      <c r="AK8" t="n">
         <v>3</v>
       </c>
       <c r="AL8" t="inlineStr">
@@ -6562,7 +6537,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" s="3">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>K4B4G1646E-BYMA</t>
@@ -6588,7 +6563,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" t="n">
         <v>14</v>
       </c>
       <c r="I9" t="inlineStr">
@@ -6606,10 +6581,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" t="n">
         <v>16</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" t="n">
         <v>3.8</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -6642,13 +6617,12 @@
           <t>28nm</t>
         </is>
       </c>
-      <c r="AB9" s="9" t="n"/>
       <c r="AF9" t="inlineStr">
         <is>
           <t>NRND</t>
         </is>
       </c>
-      <c r="AG9" s="5" t="n">
+      <c r="AG9" t="n">
         <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
@@ -6656,10 +6630,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI9" s="5" t="n">
+      <c r="AI9" t="n">
         <v>300000</v>
       </c>
-      <c r="AK9" s="5" t="n">
+      <c r="AK9" t="n">
         <v>25</v>
       </c>
       <c r="AL9" t="inlineStr">
@@ -6673,7 +6647,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" s="3">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>TLE9251VLE</t>
@@ -6704,7 +6678,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" t="n">
         <v>8</v>
       </c>
       <c r="I10" t="inlineStr">
@@ -6722,10 +6696,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" t="n">
         <v>12</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" t="n">
         <v>0.95</v>
       </c>
       <c r="N10" t="inlineStr">
@@ -6758,13 +6732,12 @@
           <t>130nm</t>
         </is>
       </c>
-      <c r="AB10" s="9" t="n"/>
       <c r="AF10" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG10" s="5" t="n">
+      <c r="AG10" t="n">
         <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
@@ -6772,7 +6745,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI10" s="5" t="n">
+      <c r="AI10" t="n">
         <v>500000</v>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -6780,7 +6753,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK10" s="5" t="n">
+      <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="inlineStr">
@@ -6794,7 +6767,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" s="3">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>1-84953-4</t>
@@ -6830,7 +6803,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
@@ -6848,10 +6821,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="8" t="n">
+      <c r="M11" t="n">
         <v>0.15</v>
       </c>
       <c r="P11" t="inlineStr">
@@ -6874,13 +6847,12 @@
           <t>Mechanical</t>
         </is>
       </c>
-      <c r="AB11" s="9" t="n"/>
       <c r="AF11" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG11" s="5" t="n">
+      <c r="AG11" t="n">
         <v>4</v>
       </c>
       <c r="AH11" t="inlineStr">
@@ -6888,10 +6860,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI11" s="5" t="n">
+      <c r="AI11" t="n">
         <v>800000</v>
       </c>
-      <c r="AK11" s="5" t="n">
+      <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="inlineStr">
@@ -6905,7 +6877,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" s="3">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>STM32F103C8T6</t>
@@ -6921,7 +6893,7 @@
           <t>MCU</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" t="n">
         <v>16</v>
       </c>
       <c r="I12" t="inlineStr">
@@ -6939,8 +6911,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="5" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
@@ -6973,13 +6944,12 @@
           <t>ST Crolles (France)</t>
         </is>
       </c>
-      <c r="AB12" s="9" t="n"/>
       <c r="AF12" t="inlineStr">
         <is>
           <t>NRND</t>
         </is>
       </c>
-      <c r="AG12" s="5" t="n">
+      <c r="AG12" t="n">
         <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
@@ -6987,10 +6957,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI12" s="5" t="n">
+      <c r="AI12" t="n">
         <v>500000</v>
       </c>
-      <c r="AK12" s="5" t="n">
+      <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="inlineStr">
@@ -7004,7 +6974,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" s="3">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>ATMEGA328P-PU</t>
@@ -7020,7 +6990,7 @@
           <t>MCU</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" t="n">
         <v>18</v>
       </c>
       <c r="I13" t="inlineStr">
@@ -7038,8 +7008,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="5" t="n">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
@@ -7072,13 +7041,12 @@
           <t>Atmel Nantes (France)</t>
         </is>
       </c>
-      <c r="AB13" s="9" t="n"/>
       <c r="AF13" t="inlineStr">
         <is>
           <t>NRND</t>
         </is>
       </c>
-      <c r="AG13" s="5" t="n">
+      <c r="AG13" t="n">
         <v>1</v>
       </c>
       <c r="AH13" t="inlineStr">
@@ -7086,10 +7054,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI13" s="5" t="n">
+      <c r="AI13" t="n">
         <v>400000</v>
       </c>
-      <c r="AK13" s="5" t="n">
+      <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="inlineStr">
@@ -7103,7 +7071,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" s="3">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>ESP32-WROOM-32</t>
@@ -7119,7 +7087,7 @@
           <t>MCU</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" t="n">
         <v>12</v>
       </c>
       <c r="I14" t="inlineStr">
@@ -7137,8 +7105,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="5" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
@@ -7171,13 +7138,12 @@
           <t>TSMC (Taiwan)</t>
         </is>
       </c>
-      <c r="AB14" s="9" t="n"/>
       <c r="AF14" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="AG14" s="5" t="n">
+      <c r="AG14" t="n">
         <v>1</v>
       </c>
       <c r="AH14" t="inlineStr">
@@ -7185,10 +7151,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AI14" s="5" t="n">
+      <c r="AI14" t="n">
         <v>250000</v>
       </c>
-      <c r="AK14" s="5" t="n">
+      <c r="AK14" t="n">
         <v>15</v>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7202,7 +7168,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" s="3">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>S32K344</t>
@@ -7233,7 +7199,7 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" t="n">
         <v>22</v>
       </c>
       <c r="I15" t="inlineStr">
@@ -7251,10 +7217,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" t="n">
         <v>28</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" t="n">
         <v>8.5</v>
       </c>
       <c r="N15" t="inlineStr">
@@ -7269,7 +7235,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:51</t>
+          <t>2026-03-01 20:17:44</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7317,7 +7283,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB15" s="5" t="n">
+      <c r="AB15" t="n">
         <v>1024</v>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7335,7 +7301,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG15" s="5" t="n">
+      <c r="AG15" t="n">
         <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
@@ -7343,7 +7309,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI15" s="5" t="n">
+      <c r="AI15" t="n">
         <v>500000</v>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -7351,7 +7317,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK15" s="5" t="n">
+      <c r="AK15" t="n">
         <v>8</v>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7365,7 +7331,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" s="3">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>S32G274A</t>
@@ -7391,7 +7357,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" t="n">
         <v>26</v>
       </c>
       <c r="I16" t="inlineStr">
@@ -7409,10 +7375,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" t="n">
         <v>36</v>
       </c>
-      <c r="M16" s="5" t="n">
+      <c r="M16" t="n">
         <v>28</v>
       </c>
       <c r="N16" t="inlineStr">
@@ -7432,7 +7398,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:51</t>
+          <t>2026-03-01 20:17:45</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7475,7 +7441,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB16" s="5" t="n">
+      <c r="AB16" t="n">
         <v>4096</v>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7493,7 +7459,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG16" s="5" t="n">
+      <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
@@ -7501,7 +7467,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI16" s="5" t="n">
+      <c r="AI16" t="n">
         <v>400000</v>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -7509,7 +7475,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK16" s="5" t="n">
+      <c r="AK16" t="n">
         <v>15</v>
       </c>
       <c r="AL16" t="inlineStr">
@@ -7523,7 +7489,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" s="3">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>PF5024</t>
@@ -7549,7 +7515,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" t="n">
         <v>20</v>
       </c>
       <c r="I17" t="inlineStr">
@@ -7567,10 +7533,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" t="n">
         <v>24</v>
       </c>
-      <c r="M17" s="8" t="n">
+      <c r="M17" t="n">
         <v>5.8</v>
       </c>
       <c r="N17" t="inlineStr">
@@ -7590,7 +7556,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:52</t>
+          <t>2026-03-01 20:17:46</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7633,7 +7599,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB17" s="5" t="n">
+      <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7641,7 +7607,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG17" s="5" t="n">
+      <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
@@ -7649,7 +7615,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI17" s="5" t="n">
+      <c r="AI17" t="n">
         <v>600000</v>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -7657,7 +7623,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK17" s="5" t="n">
+      <c r="AK17" t="n">
         <v>5</v>
       </c>
       <c r="AL17" t="inlineStr">
@@ -7671,7 +7637,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" s="3">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>EYEQ5H</t>
@@ -7697,7 +7663,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" t="n">
         <v>32</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -7715,10 +7681,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="L18" t="n">
         <v>48</v>
       </c>
-      <c r="M18" s="5" t="n">
+      <c r="M18" t="n">
         <v>55</v>
       </c>
       <c r="N18" t="inlineStr">
@@ -7738,7 +7704,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:52</t>
+          <t>2026-03-01 20:17:47</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7781,7 +7747,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB18" s="5" t="n">
+      <c r="AB18" t="n">
         <v>8192</v>
       </c>
       <c r="AC18" t="inlineStr">
@@ -7799,7 +7765,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG18" s="5" t="n">
+      <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
@@ -7807,7 +7773,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI18" s="5" t="n">
+      <c r="AI18" t="n">
         <v>350000</v>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7815,7 +7781,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK18" s="5" t="n">
+      <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="inlineStr">
@@ -7829,7 +7795,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" s="3">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>MT53E256M32D1DS-046</t>
@@ -7855,7 +7821,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" t="n">
         <v>18</v>
       </c>
       <c r="I19" t="inlineStr">
@@ -7873,10 +7839,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L19" t="n">
         <v>16</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" t="n">
         <v>6.5</v>
       </c>
       <c r="N19" t="inlineStr">
@@ -7896,7 +7862,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:52</t>
+          <t>2026-03-01 20:17:48</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7939,7 +7905,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB19" s="5" t="n">
+      <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="inlineStr">
@@ -7952,7 +7918,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG19" s="5" t="n">
+      <c r="AG19" t="n">
         <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
@@ -7960,7 +7926,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI19" s="5" t="n">
+      <c r="AI19" t="n">
         <v>200000</v>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -7968,7 +7934,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK19" s="5" t="n">
+      <c r="AK19" t="n">
         <v>30</v>
       </c>
       <c r="AL19" t="inlineStr">
@@ -7982,7 +7948,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" s="3">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>MX25U25645G</t>
@@ -8008,7 +7974,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" t="n">
         <v>14</v>
       </c>
       <c r="I20" t="inlineStr">
@@ -8026,10 +7992,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L20" t="n">
         <v>12</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" t="n">
         <v>2.8</v>
       </c>
       <c r="N20" t="inlineStr">
@@ -8044,7 +8010,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:52</t>
+          <t>2026-03-01 20:17:49</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8087,7 +8053,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB20" s="5" t="n">
+      <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8095,7 +8061,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG20" s="5" t="n">
+      <c r="AG20" t="n">
         <v>3</v>
       </c>
       <c r="AH20" t="inlineStr">
@@ -8103,7 +8069,7 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AI20" s="5" t="n">
+      <c r="AI20" t="n">
         <v>300000</v>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -8111,7 +8077,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK20" s="5" t="n">
+      <c r="AK20" t="n">
         <v>10</v>
       </c>
       <c r="AL20" t="inlineStr">
@@ -8125,7 +8091,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" s="3">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>88Q2112-A2-NNP2I000</t>
@@ -8151,7 +8117,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" t="n">
         <v>24</v>
       </c>
       <c r="I21" t="inlineStr">
@@ -8169,10 +8135,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="L21" t="n">
         <v>20</v>
       </c>
-      <c r="M21" s="8" t="n">
+      <c r="M21" t="n">
         <v>4.2</v>
       </c>
       <c r="N21" t="inlineStr">
@@ -8187,7 +8153,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:53</t>
+          <t>2026-03-01 20:17:50</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8230,7 +8196,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB21" s="5" t="n">
+      <c r="AB21" t="n">
         <v>64</v>
       </c>
       <c r="AC21" t="inlineStr">
@@ -8248,7 +8214,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG21" s="5" t="n">
+      <c r="AG21" t="n">
         <v>1</v>
       </c>
       <c r="AH21" t="inlineStr">
@@ -8256,7 +8222,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI21" s="5" t="n">
+      <c r="AI21" t="n">
         <v>450000</v>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -8264,7 +8230,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK21" s="5" t="n">
+      <c r="AK21" t="n">
         <v>12</v>
       </c>
       <c r="AL21" t="inlineStr">
@@ -8278,7 +8244,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" s="3">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>TPS65263-1QRGZRQ1</t>
@@ -8309,7 +8275,7 @@
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" t="n">
         <v>12</v>
       </c>
       <c r="I22" t="inlineStr">
@@ -8327,10 +8293,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L22" t="n">
         <v>10</v>
       </c>
-      <c r="M22" s="8" t="n">
+      <c r="M22" t="n">
         <v>3.5</v>
       </c>
       <c r="N22" t="inlineStr">
@@ -8345,7 +8311,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:53</t>
+          <t>2026-03-01 20:17:51</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8393,7 +8359,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB22" s="5" t="n">
+      <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="inlineStr">
@@ -8401,7 +8367,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG22" s="5" t="n">
+      <c r="AG22" t="n">
         <v>3</v>
       </c>
       <c r="AH22" t="inlineStr">
@@ -8409,7 +8375,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI22" s="5" t="n">
+      <c r="AI22" t="n">
         <v>700000</v>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -8417,7 +8383,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK22" s="5" t="n">
+      <c r="AK22" t="n">
         <v>3</v>
       </c>
       <c r="AL22" t="inlineStr">
@@ -8431,7 +8397,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" s="3">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>SMI230</t>
@@ -8457,7 +8423,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" t="n">
         <v>16</v>
       </c>
       <c r="I23" t="inlineStr">
@@ -8475,10 +8441,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" t="n">
         <v>14</v>
       </c>
-      <c r="M23" s="8" t="n">
+      <c r="M23" t="n">
         <v>3.8</v>
       </c>
       <c r="N23" t="inlineStr">
@@ -8493,7 +8459,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:53</t>
+          <t>2026-03-01 20:17:52</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8536,7 +8502,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB23" s="5" t="n">
+      <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="inlineStr">
@@ -8544,7 +8510,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG23" s="5" t="n">
+      <c r="AG23" t="n">
         <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
@@ -8552,7 +8518,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI23" s="5" t="n">
+      <c r="AI23" t="n">
         <v>350000</v>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -8560,7 +8526,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK23" s="5" t="n">
+      <c r="AK23" t="n">
         <v>0</v>
       </c>
       <c r="AL23" t="inlineStr">
@@ -8574,7 +8540,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" s="3">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>TJA1463</t>
@@ -8600,7 +8566,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" t="n">
         <v>18</v>
       </c>
       <c r="I24" t="inlineStr">
@@ -8618,10 +8584,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" t="n">
         <v>16</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" t="n">
         <v>2.9</v>
       </c>
       <c r="N24" t="inlineStr">
@@ -8636,7 +8602,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:53</t>
+          <t>2026-03-01 20:17:53</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8679,7 +8645,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB24" s="5" t="n">
+      <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="inlineStr">
@@ -8687,7 +8653,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG24" s="5" t="n">
+      <c r="AG24" t="n">
         <v>1</v>
       </c>
       <c r="AH24" t="inlineStr">
@@ -8695,7 +8661,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI24" s="5" t="n">
+      <c r="AI24" t="n">
         <v>600000</v>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -8703,7 +8669,7 @@
           <t>AEC-Q100</t>
         </is>
       </c>
-      <c r="AK24" s="5" t="n">
+      <c r="AK24" t="n">
         <v>5</v>
       </c>
       <c r="AL24" t="inlineStr">
@@ -8717,7 +8683,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" s="3">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>GCM32ER71E106KA37</t>
@@ -8748,7 +8714,7 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" t="n">
         <v>8</v>
       </c>
       <c r="I25" t="inlineStr">
@@ -8766,10 +8732,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="M25" s="8" t="n">
+      <c r="M25" t="n">
         <v>0.08</v>
       </c>
       <c r="N25" t="inlineStr">
@@ -8784,7 +8750,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:53</t>
+          <t>2026-03-01 20:17:53</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8832,7 +8798,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB25" s="5" t="n">
+      <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AF25" t="inlineStr">
@@ -8840,7 +8806,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG25" s="5" t="n">
+      <c r="AG25" t="n">
         <v>4</v>
       </c>
       <c r="AH25" t="inlineStr">
@@ -8848,7 +8814,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI25" s="5" t="n">
+      <c r="AI25" t="n">
         <v>1000000</v>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -8856,7 +8822,7 @@
           <t>AEC-Q200</t>
         </is>
       </c>
-      <c r="AK25" s="5" t="n">
+      <c r="AK25" t="n">
         <v>0</v>
       </c>
       <c r="AL25" t="inlineStr">
@@ -8870,7 +8836,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" s="3">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>PESD2CAN-U</t>
@@ -8901,7 +8867,7 @@
           <t>Philippines</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="inlineStr">
@@ -8919,10 +8885,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L26" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" t="n">
         <v>0.12</v>
       </c>
       <c r="N26" t="inlineStr">
@@ -8937,7 +8903,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:54</t>
+          <t>2026-03-01 20:17:54</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -8985,7 +8951,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB26" s="5" t="n">
+      <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="inlineStr">
@@ -8993,7 +8959,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG26" s="5" t="n">
+      <c r="AG26" t="n">
         <v>3</v>
       </c>
       <c r="AH26" t="inlineStr">
@@ -9001,7 +8967,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI26" s="5" t="n">
+      <c r="AI26" t="n">
         <v>800000</v>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -9009,7 +8975,7 @@
           <t>AEC-Q101</t>
         </is>
       </c>
-      <c r="AK26" s="5" t="n">
+      <c r="AK26" t="n">
         <v>0</v>
       </c>
       <c r="AL26" t="inlineStr">
@@ -9023,7 +8989,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" s="3">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>VLS252015HBX-1R0M</t>
@@ -9049,7 +9015,7 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" t="n">
         <v>8</v>
       </c>
       <c r="I27" t="inlineStr">
@@ -9067,10 +9033,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" t="n">
         <v>3</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" t="n">
         <v>0.15</v>
       </c>
       <c r="N27" t="inlineStr">
@@ -9085,7 +9051,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:54</t>
+          <t>2026-03-01 20:17:55</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9128,7 +9094,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB27" s="5" t="n">
+      <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="inlineStr">
@@ -9136,7 +9102,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG27" s="5" t="n">
+      <c r="AG27" t="n">
         <v>5</v>
       </c>
       <c r="AH27" t="inlineStr">
@@ -9144,7 +9110,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI27" s="5" t="n">
+      <c r="AI27" t="n">
         <v>900000</v>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -9152,7 +9118,7 @@
           <t>AEC-Q200</t>
         </is>
       </c>
-      <c r="AK27" s="5" t="n">
+      <c r="AK27" t="n">
         <v>0</v>
       </c>
       <c r="AL27" t="inlineStr">
@@ -9166,7 +9132,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" s="3">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>5025781070</t>
@@ -9192,7 +9158,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" t="n">
         <v>6</v>
       </c>
       <c r="I28" t="inlineStr">
@@ -9210,10 +9176,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" t="n">
         <v>0.45</v>
       </c>
       <c r="P28" t="inlineStr">
@@ -9223,7 +9189,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:54</t>
+          <t>2026-03-01 20:17:55</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9261,7 +9227,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB28" s="5" t="n">
+      <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="inlineStr">
@@ -9269,7 +9235,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG28" s="5" t="n">
+      <c r="AG28" t="n">
         <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
@@ -9277,10 +9243,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI28" s="5" t="n">
+      <c r="AI28" t="n">
         <v>500000</v>
       </c>
-      <c r="AK28" s="5" t="n">
+      <c r="AK28" t="n">
         <v>0</v>
       </c>
       <c r="AL28" t="inlineStr">
@@ -9294,7 +9260,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" s="3">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>1-2141530-1-AUT</t>
@@ -9330,7 +9296,7 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" t="n">
         <v>8</v>
       </c>
       <c r="I29" t="inlineStr">
@@ -9348,10 +9314,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M29" t="n">
         <v>0.85</v>
       </c>
       <c r="N29" t="inlineStr">
@@ -9366,7 +9332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 10:54:54</t>
+          <t>2026-03-01 20:17:56</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -9414,7 +9380,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="AB29" s="5" t="n">
+      <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AF29" t="inlineStr">
@@ -9422,7 +9388,7 @@
           <t>NRND</t>
         </is>
       </c>
-      <c r="AG29" s="5" t="n">
+      <c r="AG29" t="n">
         <v>1</v>
       </c>
       <c r="AH29" t="inlineStr">
@@ -9430,7 +9396,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI29" s="5" t="n">
+      <c r="AI29" t="n">
         <v>600000</v>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -9438,7 +9404,7 @@
           <t>AEC-Q200</t>
         </is>
       </c>
-      <c r="AK29" s="5" t="n">
+      <c r="AK29" t="n">
         <v>15</v>
       </c>
       <c r="AL29" t="inlineStr">
@@ -9452,7 +9418,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" s="3">
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>R9A07G044L23GBG</t>
@@ -9478,7 +9444,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" t="n">
         <v>20</v>
       </c>
       <c r="I30" t="inlineStr">
@@ -9496,10 +9462,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30" t="n">
         <v>24</v>
       </c>
-      <c r="M30" s="5" t="n">
+      <c r="M30" t="n">
         <v>15</v>
       </c>
       <c r="N30" t="inlineStr">
@@ -9562,7 +9528,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB30" s="5" t="n">
+      <c r="AB30" t="n">
         <v>4096</v>
       </c>
       <c r="AC30" t="inlineStr">
@@ -9580,7 +9546,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG30" s="5" t="n">
+      <c r="AG30" t="n">
         <v>1</v>
       </c>
       <c r="AH30" t="inlineStr">
@@ -9588,10 +9554,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI30" s="5" t="n">
+      <c r="AI30" t="n">
         <v>350000</v>
       </c>
-      <c r="AK30" s="5" t="n">
+      <c r="AK30" t="n">
         <v>10</v>
       </c>
       <c r="AL30" t="inlineStr">
@@ -9605,7 +9571,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" s="3">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>RAA215300</t>
@@ -9631,7 +9597,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" t="n">
         <v>18</v>
       </c>
       <c r="I31" t="inlineStr">
@@ -9649,10 +9615,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L31" t="n">
         <v>20</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" t="n">
         <v>3.5</v>
       </c>
       <c r="N31" t="inlineStr">
@@ -9715,7 +9681,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB31" s="5" t="n">
+      <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="inlineStr">
@@ -9723,7 +9689,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG31" s="5" t="n">
+      <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
@@ -9731,10 +9697,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI31" s="5" t="n">
+      <c r="AI31" t="n">
         <v>500000</v>
       </c>
-      <c r="AK31" s="5" t="n">
+      <c r="AK31" t="n">
         <v>5</v>
       </c>
       <c r="AL31" t="inlineStr">
@@ -9748,7 +9714,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" s="3">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>QCA6174A-5</t>
@@ -9774,7 +9740,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" t="n">
         <v>22</v>
       </c>
       <c r="I32" t="inlineStr">
@@ -9792,10 +9758,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" t="n">
         <v>18</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" t="n">
         <v>8.9</v>
       </c>
       <c r="N32" t="inlineStr">
@@ -9853,7 +9819,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB32" s="5" t="n">
+      <c r="AB32" t="n">
         <v>2048</v>
       </c>
       <c r="AD32" t="inlineStr">
@@ -9871,7 +9837,7 @@
           <t>NRND</t>
         </is>
       </c>
-      <c r="AG32" s="5" t="n">
+      <c r="AG32" t="n">
         <v>1</v>
       </c>
       <c r="AH32" t="inlineStr">
@@ -9879,10 +9845,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI32" s="5" t="n">
+      <c r="AI32" t="n">
         <v>300000</v>
       </c>
-      <c r="AK32" s="5" t="n">
+      <c r="AK32" t="n">
         <v>25</v>
       </c>
       <c r="AL32" t="inlineStr">
@@ -9896,7 +9862,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" s="3">
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>EC25-E</t>
@@ -9922,7 +9888,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" t="n">
         <v>14</v>
       </c>
       <c r="I33" t="inlineStr">
@@ -9940,10 +9906,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" t="n">
         <v>16</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" t="n">
         <v>18.5</v>
       </c>
       <c r="N33" t="inlineStr">
@@ -10001,7 +9967,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB33" s="5" t="n">
+      <c r="AB33" t="n">
         <v>512</v>
       </c>
       <c r="AD33" t="inlineStr">
@@ -10019,7 +9985,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG33" s="5" t="n">
+      <c r="AG33" t="n">
         <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
@@ -10027,10 +9993,10 @@
           <t>B</t>
         </is>
       </c>
-      <c r="AI33" s="5" t="n">
+      <c r="AI33" t="n">
         <v>200000</v>
       </c>
-      <c r="AK33" s="5" t="n">
+      <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="inlineStr">
@@ -10044,7 +10010,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="18.75" customHeight="1" s="3">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>MT29F4G08ABAFAWP</t>
@@ -10070,7 +10036,7 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" t="n">
         <v>16</v>
       </c>
       <c r="I34" t="inlineStr">
@@ -10088,10 +10054,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34" t="n">
         <v>8</v>
       </c>
-      <c r="M34" s="8" t="n">
+      <c r="M34" t="n">
         <v>3.2</v>
       </c>
       <c r="P34" t="inlineStr">
@@ -10144,7 +10110,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB34" s="5" t="n">
+      <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="inlineStr">
@@ -10152,7 +10118,7 @@
           <t>Last_Buy</t>
         </is>
       </c>
-      <c r="AG34" s="5" t="n">
+      <c r="AG34" t="n">
         <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
@@ -10160,10 +10126,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI34" s="5" t="n">
+      <c r="AI34" t="n">
         <v>250000</v>
       </c>
-      <c r="AK34" s="5" t="n">
+      <c r="AK34" t="n">
         <v>40</v>
       </c>
       <c r="AL34" t="inlineStr">
@@ -10177,7 +10143,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="18.75" customHeight="1" s="3">
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>AS4C256M16D3C-12</t>
@@ -10203,7 +10169,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" t="n">
         <v>14</v>
       </c>
       <c r="I35" t="inlineStr">
@@ -10221,10 +10187,10 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L35" t="n">
         <v>12</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" t="n">
         <v>2.8</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -10282,7 +10248,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB35" s="5" t="n">
+      <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="inlineStr">
@@ -10295,7 +10261,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG35" s="5" t="n">
+      <c r="AG35" t="n">
         <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
@@ -10303,10 +10269,10 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AI35" s="5" t="n">
+      <c r="AI35" t="n">
         <v>200000</v>
       </c>
-      <c r="AK35" s="5" t="n">
+      <c r="AK35" t="n">
         <v>18</v>
       </c>
       <c r="AL35" t="inlineStr">
@@ -10320,7 +10286,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" s="3">
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>LAN9250</t>
@@ -10346,7 +10312,7 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" t="n">
         <v>28</v>
       </c>
       <c r="I36" t="inlineStr">
@@ -10364,10 +10330,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="L36" t="n">
         <v>14</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" t="n">
         <v>4.5</v>
       </c>
       <c r="N36" t="inlineStr">
@@ -10425,7 +10391,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB36" s="5" t="n">
+      <c r="AB36" t="n">
         <v>256</v>
       </c>
       <c r="AC36" t="inlineStr">
@@ -10443,7 +10409,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG36" s="5" t="n">
+      <c r="AG36" t="n">
         <v>1</v>
       </c>
       <c r="AH36" t="inlineStr">
@@ -10451,10 +10417,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI36" s="5" t="n">
+      <c r="AI36" t="n">
         <v>400000</v>
       </c>
-      <c r="AK36" s="5" t="n">
+      <c r="AK36" t="n">
         <v>55</v>
       </c>
       <c r="AL36" t="inlineStr">
@@ -10468,7 +10434,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" s="3">
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>SI7021-A20-GM1R</t>
@@ -10494,7 +10460,7 @@
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" t="n">
         <v>10</v>
       </c>
       <c r="I37" t="inlineStr">
@@ -10512,10 +10478,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="M37" s="8" t="n">
+      <c r="M37" t="n">
         <v>2.1</v>
       </c>
       <c r="P37" t="inlineStr">
@@ -10568,7 +10534,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB37" s="5" t="n">
+      <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="inlineStr">
@@ -10576,7 +10542,7 @@
           <t>EOL</t>
         </is>
       </c>
-      <c r="AG37" s="5" t="n">
+      <c r="AG37" t="n">
         <v>3</v>
       </c>
       <c r="AH37" t="inlineStr">
@@ -10584,10 +10550,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI37" s="5" t="n">
+      <c r="AI37" t="n">
         <v>300000</v>
       </c>
-      <c r="AK37" s="5" t="n">
+      <c r="AK37" t="n">
         <v>0</v>
       </c>
       <c r="AL37" t="inlineStr">
@@ -10601,7 +10567,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="18.75" customHeight="1" s="3">
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>C2012X7R1H104K</t>
@@ -10632,7 +10598,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" t="n">
         <v>6</v>
       </c>
       <c r="I38" t="inlineStr">
@@ -10650,10 +10616,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="L38" t="n">
         <v>2</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" t="n">
         <v>0.01</v>
       </c>
       <c r="P38" t="inlineStr">
@@ -10711,7 +10677,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB38" s="5" t="n">
+      <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="inlineStr">
@@ -10719,7 +10685,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG38" s="5" t="n">
+      <c r="AG38" t="n">
         <v>5</v>
       </c>
       <c r="AH38" t="inlineStr">
@@ -10727,10 +10693,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI38" s="5" t="n">
+      <c r="AI38" t="n">
         <v>1000000</v>
       </c>
-      <c r="AK38" s="5" t="n">
+      <c r="AK38" t="n">
         <v>0</v>
       </c>
       <c r="AL38" t="inlineStr">
@@ -10744,7 +10710,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="18.75" customHeight="1" s="3">
+    <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>744043100</t>
@@ -10770,7 +10736,7 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" t="n">
         <v>10</v>
       </c>
       <c r="I39" t="inlineStr">
@@ -10788,10 +10754,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="L39" t="n">
         <v>4</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" t="n">
         <v>0.65</v>
       </c>
       <c r="P39" t="inlineStr">
@@ -10844,7 +10810,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB39" s="5" t="n">
+      <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="inlineStr">
@@ -10852,7 +10818,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG39" s="5" t="n">
+      <c r="AG39" t="n">
         <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
@@ -10860,10 +10826,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI39" s="5" t="n">
+      <c r="AI39" t="n">
         <v>800000</v>
       </c>
-      <c r="AK39" s="5" t="n">
+      <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="inlineStr">
@@ -10877,7 +10843,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="18.75" customHeight="1" s="3">
+    <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>10118194-0001LF</t>
@@ -10903,7 +10869,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" t="n">
         <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
@@ -10921,10 +10887,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="L40" t="n">
         <v>3</v>
       </c>
-      <c r="M40" s="8" t="n">
+      <c r="M40" t="n">
         <v>0.55</v>
       </c>
       <c r="P40" t="inlineStr">
@@ -10972,7 +10938,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB40" s="5" t="n">
+      <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AF40" t="inlineStr">
@@ -10980,7 +10946,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG40" s="5" t="n">
+      <c r="AG40" t="n">
         <v>4</v>
       </c>
       <c r="AH40" t="inlineStr">
@@ -10988,10 +10954,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI40" s="5" t="n">
+      <c r="AI40" t="n">
         <v>500000</v>
       </c>
-      <c r="AK40" s="5" t="n">
+      <c r="AK40" t="n">
         <v>5</v>
       </c>
       <c r="AL40" t="inlineStr">
@@ -11005,7 +10971,7 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="18.75" customHeight="1" s="3">
+    <row r="41">
       <c r="A41" t="inlineStr">
         <is>
           <t>IHLP2525CZER1R0M11</t>
@@ -11031,7 +10997,7 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" t="n">
         <v>8</v>
       </c>
       <c r="I41" t="inlineStr">
@@ -11049,10 +11015,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="L41" t="n">
         <v>3</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" t="n">
         <v>0.35</v>
       </c>
       <c r="P41" t="inlineStr">
@@ -11105,7 +11071,7 @@
           <t>China</t>
         </is>
       </c>
-      <c r="AB41" s="5" t="n">
+      <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AF41" t="inlineStr">
@@ -11113,7 +11079,7 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="AG41" s="5" t="n">
+      <c r="AG41" t="n">
         <v>4</v>
       </c>
       <c r="AH41" t="inlineStr">
@@ -11121,10 +11087,10 @@
           <t>A</t>
         </is>
       </c>
-      <c r="AI41" s="5" t="n">
+      <c r="AI41" t="n">
         <v>700000</v>
       </c>
-      <c r="AK41" s="5" t="n">
+      <c r="AK41" t="n">
         <v>0</v>
       </c>
       <c r="AL41" t="inlineStr">
@@ -11139,57 +11105,52 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="1" max="2"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="9" min="3" max="4"/>
-    <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="5" max="6"/>
-  </cols>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1" s="3">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Client_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>Part Number</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t>How Many Device of this specific PN are in the BOM?</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>If Dedicated Buffer Stock Units to the supplier is yes specify the number of Units</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="33" t="inlineStr">
         <is>
           <t>Custom Supplier Lead Time (weeks)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="33" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="18.75" customHeight="1" s="3">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11200,19 +11161,20 @@
           <t>MKE02Z64VLD4</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" t="n">
         <v>50000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18.75" customHeight="1" s="3">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11223,19 +11185,20 @@
           <t>STM32MP157CAC3</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18.75" customHeight="1" s="3">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11246,19 +11209,20 @@
           <t>STPMIC1APQR</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" t="n">
         <v>10000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18.75" customHeight="1" s="3">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11269,19 +11233,20 @@
           <t>BME280</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" t="n">
         <v>200000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18.75" customHeight="1" s="3">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11292,19 +11257,20 @@
           <t>ESP32-WROOM-32E</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18.75" customHeight="1" s="3">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11315,19 +11281,20 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" t="n">
         <v>45</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" t="n">
         <v>5000000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18.75" customHeight="1" s="3">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11338,19 +11305,20 @@
           <t>TPS62840DLCR</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" t="n">
         <v>150000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18.75" customHeight="1" s="3">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11361,19 +11329,20 @@
           <t>K4B4G1646E-BYMA</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" t="n">
         <v>0</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18.75" customHeight="1" s="3">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11384,19 +11353,20 @@
           <t>TLE9251VLE</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" t="n">
         <v>100000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18.75" customHeight="1" s="3">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>DEMO_CLIENT</t>
@@ -11407,19 +11377,20 @@
           <t>1-84953-4</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" t="n">
         <v>8</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" t="n">
         <v>1000000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18.75" customHeight="1" s="3">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11430,19 +11401,20 @@
           <t>S32K344</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" t="n">
         <v>75000</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18.75" customHeight="1" s="3">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11453,19 +11425,20 @@
           <t>S32G274A</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" t="n">
         <v>0</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18.75" customHeight="1" s="3">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11476,19 +11449,20 @@
           <t>PF5024</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" t="n">
         <v>15000</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18.75" customHeight="1" s="3">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11499,19 +11473,20 @@
           <t>EYEQ5H</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" t="n">
         <v>0</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18.75" customHeight="1" s="3">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11522,19 +11497,20 @@
           <t>MT53E256M32D1DS-046</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18.75" customHeight="1" s="3">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11545,19 +11521,20 @@
           <t>MX25U25645G</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" t="n">
         <v>40000</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18.75" customHeight="1" s="3">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11568,19 +11545,20 @@
           <t>88Q2112-A2-NNP2I000</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" t="n">
         <v>25000</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18.75" customHeight="1" s="3">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11591,19 +11569,20 @@
           <t>TPS65263-1QRGZRQ1</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" t="n">
         <v>80000</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18.75" customHeight="1" s="3">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11614,19 +11593,20 @@
           <t>SMI230</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" t="n">
         <v>30000</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18.75" customHeight="1" s="3">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11637,19 +11617,20 @@
           <t>TJA1463</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" t="n">
         <v>60000</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18.75" customHeight="1" s="3">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11660,19 +11641,20 @@
           <t>GCM32ER71E106KA37</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" t="n">
         <v>65</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" t="n">
         <v>5000000</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18.75" customHeight="1" s="3">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11683,19 +11665,20 @@
           <t>PESD2CAN-U</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" t="n">
         <v>6</v>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" t="n">
         <v>500000</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18.75" customHeight="1" s="3">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11706,19 +11689,20 @@
           <t>VLS252015HBX-1R0M</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" t="n">
         <v>800000</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="18.75" customHeight="1" s="3">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11729,19 +11713,20 @@
           <t>5025781070</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" t="n">
         <v>4</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" t="n">
         <v>200000</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18.75" customHeight="1" s="3">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>ADAS_AUTO</t>
@@ -11752,19 +11737,20 @@
           <t>1-2141530-1-AUT</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" t="n">
         <v>2</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" t="n">
         <v>200000</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18.75" customHeight="1" s="3">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11775,19 +11761,20 @@
           <t>R9A07G044L23GBG</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" t="n">
         <v>0</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18.75" customHeight="1" s="3">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11798,19 +11785,20 @@
           <t>RAA215300</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" t="n">
         <v>20000</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18.75" customHeight="1" s="3">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11821,19 +11809,20 @@
           <t>QCA6174A-5</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" t="n">
         <v>0</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18.75" customHeight="1" s="3">
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11844,19 +11833,20 @@
           <t>EC25-E</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" t="n">
         <v>15000</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18.75" customHeight="1" s="3">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11867,19 +11857,20 @@
           <t>MT29F4G08ABAFAWP</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" t="n">
         <v>0</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18.75" customHeight="1" s="3">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11890,19 +11881,20 @@
           <t>AS4C256M16D3C-12</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" t="n">
         <v>2</v>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" t="n">
         <v>30000</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18.75" customHeight="1" s="3">
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11913,19 +11905,20 @@
           <t>LAN9250</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" t="n">
         <v>8000</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18.75" customHeight="1" s="3">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11936,19 +11929,20 @@
           <t>SI7021-A20-GM1R</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" t="n">
         <v>50000</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="18.75" customHeight="1" s="3">
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11959,19 +11953,20 @@
           <t>C2012X7R1H104K</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" t="n">
         <v>120</v>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" t="n">
         <v>10000000</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="18.75" customHeight="1" s="3">
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -11982,19 +11977,20 @@
           <t>744043100</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" t="n">
         <v>4</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" t="n">
         <v>150000</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18.75" customHeight="1" s="3">
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -12005,19 +12001,20 @@
           <t>10118194-0001LF</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" t="n">
         <v>100000</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18.75" customHeight="1" s="3">
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>IOT_INDUST</t>
@@ -12028,20 +12025,321 @@
           <t>IHLP2525CZER1R0M11</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" t="n">
         <v>6</v>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" t="n">
         <v>300000</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S32K344</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>75000</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>S32G274A</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PF5024</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>EYEQ5H</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MT53E256M32D1DS-046</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MX25U25645G</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>88Q2112-A2-NNP2I000</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TPS65263-1QRGZRQ1</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>80000</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SMI230</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TJA1463</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GCM32ER71E106KA37</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>65</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PESD2CAN-U</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>VLS252015HBX-1R0M</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5025781070</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1-2141530-1-AUT</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -7235,7 +7235,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:44</t>
+          <t>2026-03-01 21:15:59</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:45</t>
+          <t>2026-03-01 21:15:59</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:46</t>
+          <t>2026-03-01 21:16:00</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:47</t>
+          <t>2026-03-01 21:16:01</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:48</t>
+          <t>2026-03-01 21:16:02</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:49</t>
+          <t>2026-03-01 21:16:03</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:50</t>
+          <t>2026-03-01 21:16:03</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:51</t>
+          <t>2026-03-01 21:16:04</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:52</t>
+          <t>2026-03-01 21:16:05</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:53</t>
+          <t>2026-03-01 21:16:06</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:53</t>
+          <t>2026-03-01 21:16:06</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:54</t>
+          <t>2026-03-01 21:16:07</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:55</t>
+          <t>2026-03-01 21:16:08</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:55</t>
+          <t>2026-03-01 21:16:09</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 20:17:56</t>
+          <t>2026-03-01 21:16:09</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -7235,7 +7235,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 21:15:59</t>
+          <t>2026-03-01 21:20:42</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 21:15:59</t>
+          <t>2026-03-01 21:20:43</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:00</t>
+          <t>2026-03-01 21:20:43</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:01</t>
+          <t>2026-03-01 21:20:44</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:02</t>
+          <t>2026-03-01 21:20:45</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:03</t>
+          <t>2026-03-01 21:20:46</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:03</t>
+          <t>2026-03-01 21:20:47</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:04</t>
+          <t>2026-03-01 21:20:47</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:05</t>
+          <t>2026-03-01 21:20:48</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:06</t>
+          <t>2026-03-01 21:20:49</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:06</t>
+          <t>2026-03-01 21:20:50</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:07</t>
+          <t>2026-03-01 21:20:51</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:08</t>
+          <t>2026-03-01 21:20:51</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:09</t>
+          <t>2026-03-01 21:20:52</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 21:16:09</t>
+          <t>2026-03-01 21:20:53</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -7235,7 +7235,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:42</t>
+          <t>2026-03-01 21:23:57</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:43</t>
+          <t>2026-03-01 21:23:57</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:43</t>
+          <t>2026-03-01 21:23:58</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:44</t>
+          <t>2026-03-01 21:23:58</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:45</t>
+          <t>2026-03-01 21:23:59</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:46</t>
+          <t>2026-03-01 21:24:00</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:47</t>
+          <t>2026-03-01 21:24:00</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:47</t>
+          <t>2026-03-01 21:24:01</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:48</t>
+          <t>2026-03-01 21:24:02</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:49</t>
+          <t>2026-03-01 21:24:03</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:50</t>
+          <t>2026-03-01 21:24:04</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:51</t>
+          <t>2026-03-01 21:24:04</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:51</t>
+          <t>2026-03-01 21:24:05</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:52</t>
+          <t>2026-03-01 21:24:06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 21:20:53</t>
+          <t>2026-03-01 21:24:07</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -7235,7 +7235,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 21:23:57</t>
+          <t>2026-03-01 21:27:36</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 21:23:57</t>
+          <t>2026-03-01 21:27:37</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 21:23:58</t>
+          <t>2026-03-01 21:27:38</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7704,7 +7704,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 21:23:58</t>
+          <t>2026-03-01 21:27:39</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 21:23:59</t>
+          <t>2026-03-01 21:27:39</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:00</t>
+          <t>2026-03-01 21:27:40</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:00</t>
+          <t>2026-03-01 21:27:41</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:01</t>
+          <t>2026-03-01 21:27:42</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:02</t>
+          <t>2026-03-01 21:27:42</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:03</t>
+          <t>2026-03-01 21:27:43</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:04</t>
+          <t>2026-03-01 21:27:44</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:04</t>
+          <t>2026-03-01 21:27:45</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:05</t>
+          <t>2026-03-01 21:27:45</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:06</t>
+          <t>2026-03-01 21:27:46</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 21:24:07</t>
+          <t>2026-03-01 21:27:47</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alt_Sources" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier_Profiles" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP_Dependencies" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis_History" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5566,6 +5567,126 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Snapshot_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>Client_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="33" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="D1" s="33" t="inlineStr">
+        <is>
+          <t>BOM_Name</t>
+        </is>
+      </c>
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>Avg_Risk_Score</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>High_Risk_Count</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Medium_Risk_Count</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>Low_Risk_Count</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>SPOF_Count</t>
+        </is>
+      </c>
+      <c r="J1" s="33" t="inlineStr">
+        <is>
+          <t>Total_Components</t>
+        </is>
+      </c>
+      <c r="K1" s="33" t="inlineStr">
+        <is>
+          <t>BOM_Value</t>
+        </is>
+      </c>
+      <c r="L1" s="33" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SNAP_0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-01T22:23:49.177571</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K2" t="n">
+        <v>163.92</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7235,7 +7356,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:36</t>
+          <t>2026-03-01 22:23:37</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7398,7 +7519,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:37</t>
+          <t>2026-03-01 22:23:38</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7556,7 +7677,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:38</t>
+          <t>2026-03-01 22:23:38</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7704,7 +7825,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:39</t>
+          <t>2026-03-01 22:23:39</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7862,7 +7983,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:39</t>
+          <t>2026-03-01 22:23:40</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8010,7 +8131,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:40</t>
+          <t>2026-03-01 22:23:41</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8153,7 +8274,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:41</t>
+          <t>2026-03-01 22:23:42</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8311,7 +8432,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:42</t>
+          <t>2026-03-01 22:23:42</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8459,7 +8580,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:42</t>
+          <t>2026-03-01 22:23:43</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8602,7 +8723,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:43</t>
+          <t>2026-03-01 22:23:44</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8750,7 +8871,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:44</t>
+          <t>2026-03-01 22:23:45</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8903,7 +9024,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:45</t>
+          <t>2026-03-01 22:23:46</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9051,7 +9172,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:45</t>
+          <t>2026-03-01 22:23:46</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9189,7 +9310,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:46</t>
+          <t>2026-03-01 22:23:47</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9332,7 +9453,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 21:27:47</t>
+          <t>2026-03-01 22:23:48</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -11167,7 +11288,6 @@
       <c r="D2" t="n">
         <v>50000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11191,7 +11311,6 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11215,7 +11334,6 @@
       <c r="D4" t="n">
         <v>10000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11239,7 +11357,6 @@
       <c r="D5" t="n">
         <v>200000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11263,7 +11380,6 @@
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11287,7 +11403,6 @@
       <c r="D7" t="n">
         <v>5000000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11311,7 +11426,6 @@
       <c r="D8" t="n">
         <v>150000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11335,7 +11449,6 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11359,7 +11472,6 @@
       <c r="D10" t="n">
         <v>100000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11383,7 +11495,6 @@
       <c r="D11" t="n">
         <v>1000000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Importato dal template di esempio</t>
@@ -11407,7 +11518,6 @@
       <c r="D12" t="n">
         <v>75000</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11431,7 +11541,6 @@
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11455,7 +11564,6 @@
       <c r="D14" t="n">
         <v>15000</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11479,7 +11587,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11503,7 +11610,6 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11527,7 +11633,6 @@
       <c r="D17" t="n">
         <v>40000</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11551,7 +11656,6 @@
       <c r="D18" t="n">
         <v>25000</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11575,7 +11679,6 @@
       <c r="D19" t="n">
         <v>80000</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11599,7 +11702,6 @@
       <c r="D20" t="n">
         <v>30000</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11623,7 +11725,6 @@
       <c r="D21" t="n">
         <v>60000</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11647,7 +11748,6 @@
       <c r="D22" t="n">
         <v>5000000</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11671,7 +11771,6 @@
       <c r="D23" t="n">
         <v>500000</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11695,7 +11794,6 @@
       <c r="D24" t="n">
         <v>800000</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11719,7 +11817,6 @@
       <c r="D25" t="n">
         <v>200000</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11743,7 +11840,6 @@
       <c r="D26" t="n">
         <v>200000</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Importato da BOM ADAS_AUTO</t>
@@ -11767,7 +11863,6 @@
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11791,7 +11886,6 @@
       <c r="D28" t="n">
         <v>20000</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11815,7 +11909,6 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11839,7 +11932,6 @@
       <c r="D30" t="n">
         <v>15000</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11863,7 +11955,6 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11887,7 +11978,6 @@
       <c r="D32" t="n">
         <v>30000</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11911,7 +12001,6 @@
       <c r="D33" t="n">
         <v>8000</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11935,7 +12024,6 @@
       <c r="D34" t="n">
         <v>50000</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11959,7 +12047,6 @@
       <c r="D35" t="n">
         <v>10000000</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -11983,7 +12070,6 @@
       <c r="D36" t="n">
         <v>150000</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -12007,7 +12093,6 @@
       <c r="D37" t="n">
         <v>100000</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -12031,7 +12116,6 @@
       <c r="D38" t="n">
         <v>300000</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>Importato da BOM IOT_INDUST</t>
@@ -12055,8 +12139,6 @@
       <c r="D39" t="n">
         <v>75000</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12075,8 +12157,6 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12095,8 +12175,6 @@
       <c r="D41" t="n">
         <v>15000</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12115,8 +12193,6 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12135,8 +12211,6 @@
       <c r="D43" t="n">
         <v>0</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12155,8 +12229,6 @@
       <c r="D44" t="n">
         <v>40000</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12175,8 +12247,6 @@
       <c r="D45" t="n">
         <v>25000</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12195,8 +12265,6 @@
       <c r="D46" t="n">
         <v>80000</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12215,8 +12283,6 @@
       <c r="D47" t="n">
         <v>30000</v>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12235,8 +12301,6 @@
       <c r="D48" t="n">
         <v>60000</v>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12255,8 +12319,6 @@
       <c r="D49" t="n">
         <v>5000000</v>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12275,8 +12337,6 @@
       <c r="D50" t="n">
         <v>500000</v>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12295,8 +12355,6 @@
       <c r="D51" t="n">
         <v>800000</v>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12315,8 +12373,6 @@
       <c r="D52" t="n">
         <v>200000</v>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12335,8 +12391,6 @@
       <c r="D53" t="n">
         <v>200000</v>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier_Profiles" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IP_Dependencies" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis_History" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activity_Log" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -5573,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5680,7 +5681,594 @@
       <c r="K2" t="n">
         <v>163.92</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SNAP_0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-01T22:52:37.078780</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SNAP_0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-01T22:53:42.880944</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SNAP_0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:04:37.886965</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SNAP_0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:09:28.015537</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SNAP_0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:12:26.270143</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SNAP_0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:14:29.200541</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="n">
+        <v>163.92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Log_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>Client_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="33" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="D1" s="33" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E1" s="33" t="inlineStr">
+        <is>
+          <t>Action_Type</t>
+        </is>
+      </c>
+      <c r="F1" s="33" t="inlineStr">
+        <is>
+          <t>Target_PN</t>
+        </is>
+      </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Old_Value</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>New_Value</t>
+        </is>
+      </c>
+      <c r="I1" s="33" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LOG_0001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-01T22:52:37.431578</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LOG_0002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-01T22:53:43.251563</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LOG_0003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:04:38.280518</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LOG_0004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TEST_CLIENT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:06:57.893836</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>test log</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LOG_0005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:09:28.398109</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LOG_0006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:12:26.470330</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LOG_0007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:14:29.574188</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7356,7 +7944,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:37</t>
+          <t>2026-03-01 23:14:17</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7519,7 +8107,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:38</t>
+          <t>2026-03-01 23:14:18</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7677,7 +8265,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:38</t>
+          <t>2026-03-01 23:14:19</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7825,7 +8413,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:39</t>
+          <t>2026-03-01 23:14:20</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7983,7 +8571,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:40</t>
+          <t>2026-03-01 23:14:21</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8131,7 +8719,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:41</t>
+          <t>2026-03-01 23:14:21</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8274,7 +8862,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:42</t>
+          <t>2026-03-01 23:14:21</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8432,7 +9020,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:42</t>
+          <t>2026-03-01 23:14:22</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8580,7 +9168,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:43</t>
+          <t>2026-03-01 23:14:23</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8723,7 +9311,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:44</t>
+          <t>2026-03-01 23:14:23</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -8871,7 +9459,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:45</t>
+          <t>2026-03-01 23:14:24</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -9024,7 +9612,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:46</t>
+          <t>2026-03-01 23:14:25</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9172,7 +9760,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:46</t>
+          <t>2026-03-01 23:14:26</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9310,7 +9898,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:47</t>
+          <t>2026-03-01 23:14:27</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -9453,7 +10041,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 22:23:48</t>
+          <t>2026-03-01 23:14:28</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -5574,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5937,6 +5937,92 @@
         <v>15</v>
       </c>
       <c r="K8" t="n">
+        <v>163.92</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SNAP_0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:18:29.519324</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" t="n">
+        <v>163.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SNAP_0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:25:50.200285</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" t="n">
         <v>163.92</v>
       </c>
     </row>
@@ -5951,7 +6037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6265,6 +6351,84 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LOG_0008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:18:29.695191</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOG_0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:25:50.580387</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Batch 15 componenti</t>
         </is>
@@ -7944,7 +8108,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:17</t>
+          <t>2026-03-01 23:25:41</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -8107,7 +8271,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:18</t>
+          <t>2026-03-01 23:25:41</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -8265,7 +8429,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:19</t>
+          <t>2026-03-01 23:25:42</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -8413,7 +8577,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:20</t>
+          <t>2026-03-01 23:25:42</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -8571,7 +8735,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:21</t>
+          <t>2026-03-01 23:25:43</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8719,7 +8883,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:21</t>
+          <t>2026-03-01 23:25:43</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8862,7 +9026,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:21</t>
+          <t>2026-03-01 23:25:43</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -9020,7 +9184,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:22</t>
+          <t>2026-03-01 23:25:44</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -9168,7 +9332,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:23</t>
+          <t>2026-03-01 23:25:44</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -9311,7 +9475,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:23</t>
+          <t>2026-03-01 23:25:45</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -9459,7 +9623,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:24</t>
+          <t>2026-03-01 23:25:45</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -9612,7 +9776,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:25</t>
+          <t>2026-03-01 23:25:46</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9760,7 +9924,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:26</t>
+          <t>2026-03-01 23:25:47</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -9898,7 +10062,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:27</t>
+          <t>2026-03-01 23:25:48</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -10041,7 +10205,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 23:14:28</t>
+          <t>2026-03-01 23:25:49</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -11824,7 +11988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11858,6 +12022,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="G1" s="33" t="inlineStr">
+        <is>
+          <t>Risk_Owner</t>
+        </is>
+      </c>
+      <c r="H1" s="33" t="inlineStr">
+        <is>
+          <t>Risk_Status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11881,6 +12055,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11904,6 +12083,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11927,6 +12111,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11950,6 +12139,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11973,6 +12167,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11996,6 +12195,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12019,6 +12223,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12042,6 +12251,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12065,6 +12279,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12088,6 +12307,11 @@
           <t>Importato dal template di esempio</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -12111,6 +12335,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -12134,6 +12363,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -12157,6 +12391,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -12180,6 +12419,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -12203,6 +12447,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12226,6 +12475,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12249,6 +12503,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12272,6 +12531,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12295,6 +12559,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12318,6 +12587,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12341,6 +12615,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12364,6 +12643,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12387,6 +12671,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12410,6 +12699,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12433,6 +12727,11 @@
           <t>Importato da BOM ADAS_AUTO</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12456,6 +12755,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -12479,6 +12783,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -12502,6 +12811,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -12525,6 +12839,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -12548,6 +12867,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -12571,6 +12895,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -12594,6 +12923,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -12617,6 +12951,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -12640,6 +12979,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -12663,6 +13007,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -12686,6 +13035,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -12709,6 +13063,11 @@
           <t>Importato da BOM IOT_INDUST</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12727,6 +13086,11 @@
       <c r="D39" t="n">
         <v>75000</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12745,6 +13109,11 @@
       <c r="D40" t="n">
         <v>0</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12763,6 +13132,11 @@
       <c r="D41" t="n">
         <v>15000</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -12781,6 +13155,11 @@
       <c r="D42" t="n">
         <v>0</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12799,6 +13178,11 @@
       <c r="D43" t="n">
         <v>0</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12817,6 +13201,11 @@
       <c r="D44" t="n">
         <v>40000</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12835,6 +13224,11 @@
       <c r="D45" t="n">
         <v>25000</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12853,6 +13247,11 @@
       <c r="D46" t="n">
         <v>80000</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12871,6 +13270,11 @@
       <c r="D47" t="n">
         <v>30000</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12889,6 +13293,11 @@
       <c r="D48" t="n">
         <v>60000</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12907,6 +13316,11 @@
       <c r="D49" t="n">
         <v>5000000</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12925,6 +13339,11 @@
       <c r="D50" t="n">
         <v>500000</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -12943,6 +13362,11 @@
       <c r="D51" t="n">
         <v>800000</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12961,6 +13385,11 @@
       <c r="D52" t="n">
         <v>200000</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12978,6 +13407,11 @@
       </c>
       <c r="D53" t="n">
         <v>200000</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12991,7 +13425,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
     <col width="13.53515625" bestFit="1" customWidth="1" style="3" min="1" max="2"/>
@@ -13020,6 +13454,16 @@
           <t>Created_at</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Risk_Appetite_High</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Risk_Appetite_Medium</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="18.75" customHeight="1" s="3">
       <c r="A2" t="inlineStr">
@@ -13040,6 +13484,12 @@
           <t>2026-02-08 03:29:59</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>55</v>
+      </c>
+      <c r="F2" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="3" ht="18.75" customHeight="1" s="3">
       <c r="A3" t="inlineStr">
@@ -13060,6 +13510,12 @@
           <t>2026-02-14 20:05:35</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" ht="18.75" customHeight="1" s="3">
       <c r="A4" t="inlineStr">
@@ -13079,6 +13535,12 @@
         <is>
           <t>2026-02-14 20:05:35</t>
         </is>
+      </c>
+      <c r="E4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F4" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/part_numbers_db.xlsx
+++ b/data/part_numbers_db.xlsx
@@ -5574,7 +5574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6023,6 +6023,49 @@
         <v>15</v>
       </c>
       <c r="K10" t="n">
+        <v>163.92</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SNAP_0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:37:32.779793</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>02_BOM_Automotive_ADAS_ECU_15</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" t="n">
         <v>163.92</v>
       </c>
     </row>
@@ -6037,7 +6080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6429,6 +6472,45 @@
         </is>
       </c>
       <c r="I10" t="inlineStr">
+        <is>
+          <t>Batch 15 componenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOG_0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEMO_CLIENT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-01T23:37:33.178154</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>risk_analysis</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BOM=02_BOM_Automotive_ADAS_ECU_15, HIGH=9</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>Batch 15 componenti</t>
         </is>
@@ -8108,7 +8190,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:41</t>
+          <t>2026-03-01 23:37:19</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -8271,7 +8353,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:41</t>
+          <t>2026-03-01 23:37:20</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -8429,7 +8511,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:42</t>
+          <t>2026-03-01 23:37:21</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -8577,7 +8659,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:42</t>
+          <t>2026-03-01 23:37:22</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -8735,7 +8817,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:43</t>
+          <t>2026-03-01 23:37:23</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8883,7 +8965,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:43</t>
+          <t>2026-03-01 23:37:23</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -9026,7 +9108,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:43</t>
+          <t>2026-03-01 23:37:24</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -9184,7 +9266,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:44</t>
+          <t>2026-03-01 23:37:25</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -9332,7 +9414,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:44</t>
+          <t>2026-03-01 23:37:26</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -9475,7 +9557,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:45</t>
+          <t>2026-03-01 23:37:27</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -9623,7 +9705,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:45</t>
+          <t>2026-03-01 23:37:28</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -9776,7 +9858,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:46</t>
+          <t>2026-03-01 23:37:29</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -9924,7 +10006,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:47</t>
+          <t>2026-03-01 23:37:30</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -10062,7 +10144,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:48</t>
+          <t>2026-03-01 23:37:31</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -10205,7 +10287,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2026-03-01 23:25:49</t>
+          <t>2026-03-01 23:37:31</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
